--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -864,7 +864,7 @@
     <t>Plan/proposal/order fulfilled by this request.</t>
   </si>
   <si>
-    <t>Written as ServiceRequest/{external order number}: the order number (the first identifier value of the incoming ServiceRequest), not the incoming ServiceRequest's id. All tests of the order carry the same value (see Known Issues).</t>
+    <t>The incoming ServiceRequest by id, found through OpenELIS's local copy of it. When that copy cannot be read, a logical reference: type ServiceRequest with the order number (the incoming ServiceRequest's first identifier value) as identifier.value.</t>
   </si>
   <si>
     <t>Sample.referringId (external order number)</t>
@@ -1275,7 +1275,7 @@
     <t>ServiceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://digi-uw.github.io/openelis-global2-fhir-ig/StructureDefinition/openelis-patient)
+    <t xml:space="preserve">Reference(https://digi-uw.github.io/openelis-global2-fhir-ig/StructureDefinition/openelis-patient|https://digi-uw.github.io/openelis-global2-fhir-ig/StructureDefinition/openelis-site-location|Group)
 </t>
   </si>
   <si>
@@ -1285,10 +1285,10 @@
     <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
   </si>
   <si>
-    <t>OpenELIS omits subject for environmental and vector samples, although R4 requires it (see Known Issues).</t>
-  </si>
-  <si>
-    <t>SampleHuman.patient</t>
+    <t>The Patient. An order without a patient (environmental, vector, or clinical entered without one) has the sampling site's Location (the sample item's collection site, else the order's environmental or vector site) when the site stands for an organization, else a contained Group (#subject: type substance for environmental, animal for vector, person otherwise; actual false; name = the site name when known).</t>
+  </si>
+  <si>
+    <t>SampleHuman.patient, else ObservationHistory envSamplingSiteId / vecCollectionSiteId (VectorSamplingSite.organizationId)</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1412,7 +1412,7 @@
     <t>When the request transitioned to being actionable.</t>
   </si>
   <si>
-    <t>Currently the time the resource was generated, not the order entry time (see Known Issues).</t>
+    <t>The order's request date (day precision) when recorded, else when the order was entered. The same order is published with the same value every time.</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1552,14 +1552,14 @@
     <t>ServiceRequest.locationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(https://digi-uw.github.io/openelis-global2-fhir-ig/StructureDefinition/openelis-site-location)
 </t>
   </si>
   <si>
     <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
   </si>
   <si>
-    <t>Referring site and referring department. The reference id is the OpenELIS Organization UUID written as Location/{id} (see Known Issues).</t>
+    <t>Referring site, then referring department: the site Location of each organization (same id as the Organization). OpenELIS writes those Locations to the FHIR store with the ServiceRequest and serves them from /fhir/Location/{id}.</t>
   </si>
   <si>
     <t>Sample requester organizations (referring org / referring department)</t>
@@ -2123,7 +2123,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="126.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="152.51171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2148,7 +2148,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="55.90234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="73.23046875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="140.125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
